--- a/light_fight/Assets/Excels/EquipmentConfig.xlsx
+++ b/light_fight/Assets/Excels/EquipmentConfig.xlsx
@@ -557,12 +557,8 @@
       <c r="I2" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
       <c r="L2" s="5" t="n">
         <v>61001</v>
       </c>
@@ -598,12 +594,8 @@
       <c r="I3" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
       <c r="L3" s="5" t="n">
         <v>61002</v>
       </c>
@@ -639,12 +631,8 @@
       <c r="I4" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
       <c r="L4" s="5" t="n">
         <v>61003</v>
       </c>
@@ -680,12 +668,8 @@
       <c r="I5" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
       <c r="L5" s="5" t="n">
         <v>61004</v>
       </c>
@@ -721,12 +705,8 @@
       <c r="I6" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
       <c r="L6" s="5" t="n">
         <v>61005</v>
       </c>
@@ -762,12 +742,8 @@
       <c r="I7" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
       <c r="L7" s="5" t="n">
         <v>61006</v>
       </c>
@@ -803,12 +779,8 @@
       <c r="I8" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
       <c r="L8" s="5" t="n">
         <v>61007</v>
       </c>
@@ -844,12 +816,8 @@
       <c r="I9" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
       <c r="L9" s="5" t="n">
         <v>61008</v>
       </c>
@@ -885,12 +853,8 @@
       <c r="I10" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
       <c r="L10" s="5" t="n">
         <v>61009</v>
       </c>
@@ -926,12 +890,8 @@
       <c r="I11" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
       <c r="L11" s="5" t="n">
         <v>61010</v>
       </c>
@@ -970,12 +930,8 @@
       <c r="I12" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
       <c r="L12" s="9" t="n">
         <v>61001</v>
       </c>
@@ -1011,12 +967,8 @@
       <c r="I13" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
       <c r="L13" s="9" t="n">
         <v>61002</v>
       </c>
@@ -1052,12 +1004,8 @@
       <c r="I14" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
       <c r="L14" s="9" t="n">
         <v>61003</v>
       </c>
@@ -1093,12 +1041,8 @@
       <c r="I15" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
       <c r="L15" s="9" t="n">
         <v>61004</v>
       </c>
@@ -1134,12 +1078,8 @@
       <c r="I16" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
       <c r="L16" s="9" t="n">
         <v>61005</v>
       </c>
@@ -1175,12 +1115,8 @@
       <c r="I17" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
       <c r="L17" s="9" t="n">
         <v>61006</v>
       </c>
@@ -1216,12 +1152,8 @@
       <c r="I18" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
       <c r="L18" s="9" t="n">
         <v>61007</v>
       </c>
@@ -1257,12 +1189,8 @@
       <c r="I19" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
       <c r="L19" s="9" t="n">
         <v>61008</v>
       </c>
@@ -1298,12 +1226,8 @@
       <c r="I20" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
       <c r="L20" s="9" t="n">
         <v>61009</v>
       </c>
@@ -1339,12 +1263,8 @@
       <c r="I21" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
       <c r="L21" s="9" t="n">
         <v>61010</v>
       </c>
@@ -1380,12 +1300,8 @@
       <c r="I22" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
       <c r="L22" s="5" t="n">
         <v>61001</v>
       </c>
@@ -1421,12 +1337,8 @@
       <c r="I23" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
       <c r="L23" s="5" t="n">
         <v>61002</v>
       </c>
@@ -1462,12 +1374,8 @@
       <c r="I24" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
       <c r="L24" s="5" t="n">
         <v>61003</v>
       </c>
@@ -1503,12 +1411,8 @@
       <c r="I25" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
       <c r="L25" s="5" t="n">
         <v>61004</v>
       </c>
@@ -1544,12 +1448,8 @@
       <c r="I26" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
       <c r="L26" s="5" t="n">
         <v>61005</v>
       </c>
@@ -1585,12 +1485,8 @@
       <c r="I27" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
       <c r="L27" s="5" t="n">
         <v>61006</v>
       </c>
@@ -1626,12 +1522,8 @@
       <c r="I28" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
       <c r="L28" s="5" t="n">
         <v>61007</v>
       </c>
@@ -1667,12 +1559,8 @@
       <c r="I29" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
       <c r="L29" s="5" t="n">
         <v>61008</v>
       </c>
@@ -1708,12 +1596,8 @@
       <c r="I30" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
       <c r="L30" s="5" t="n">
         <v>61009</v>
       </c>
@@ -1749,12 +1633,8 @@
       <c r="I31" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
       <c r="L31" s="5" t="n">
         <v>61010</v>
       </c>
@@ -1790,12 +1670,8 @@
       <c r="I32" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
       <c r="L32" s="9" t="n">
         <v>61001</v>
       </c>
@@ -1831,12 +1707,8 @@
       <c r="I33" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
       <c r="L33" s="9" t="n">
         <v>61002</v>
       </c>
@@ -1872,12 +1744,8 @@
       <c r="I34" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
       <c r="L34" s="9" t="n">
         <v>61003</v>
       </c>
@@ -1913,12 +1781,8 @@
       <c r="I35" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
       <c r="L35" s="9" t="n">
         <v>61004</v>
       </c>
@@ -1954,12 +1818,8 @@
       <c r="I36" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
       <c r="L36" s="9" t="n">
         <v>61005</v>
       </c>
@@ -1995,12 +1855,8 @@
       <c r="I37" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
       <c r="L37" s="9" t="n">
         <v>61006</v>
       </c>
@@ -2036,12 +1892,8 @@
       <c r="I38" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
       <c r="L38" s="9" t="n">
         <v>61007</v>
       </c>
@@ -2077,12 +1929,8 @@
       <c r="I39" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
       <c r="L39" s="9" t="n">
         <v>61008</v>
       </c>
@@ -2118,12 +1966,8 @@
       <c r="I40" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
       <c r="L40" s="9" t="n">
         <v>61009</v>
       </c>
@@ -2159,12 +2003,8 @@
       <c r="I41" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
       <c r="L41" s="9" t="n">
         <v>61010</v>
       </c>
@@ -2200,12 +2040,8 @@
       <c r="I42" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
       <c r="L42" s="5" t="n">
         <v>61001</v>
       </c>
@@ -2241,12 +2077,8 @@
       <c r="I43" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
       <c r="L43" s="5" t="n">
         <v>61002</v>
       </c>
@@ -2282,12 +2114,8 @@
       <c r="I44" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
       <c r="L44" s="5" t="n">
         <v>61003</v>
       </c>
@@ -2323,12 +2151,8 @@
       <c r="I45" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
       <c r="L45" s="5" t="n">
         <v>61004</v>
       </c>
@@ -2364,12 +2188,8 @@
       <c r="I46" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
       <c r="L46" s="5" t="n">
         <v>61005</v>
       </c>
@@ -2405,12 +2225,8 @@
       <c r="I47" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
       <c r="L47" s="5" t="n">
         <v>61006</v>
       </c>
@@ -2446,12 +2262,8 @@
       <c r="I48" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
       <c r="L48" s="5" t="n">
         <v>61007</v>
       </c>
@@ -2487,12 +2299,8 @@
       <c r="I49" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
       <c r="L49" s="5" t="n">
         <v>61008</v>
       </c>
@@ -2528,12 +2336,8 @@
       <c r="I50" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
       <c r="L50" s="5" t="n">
         <v>61009</v>
       </c>
@@ -2569,12 +2373,8 @@
       <c r="I51" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
       <c r="L51" s="5" t="n">
         <v>61010</v>
       </c>
@@ -2610,12 +2410,8 @@
       <c r="I52" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
       <c r="L52" s="9" t="n">
         <v>61001</v>
       </c>
@@ -2651,12 +2447,8 @@
       <c r="I53" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
       <c r="L53" s="9" t="n">
         <v>61002</v>
       </c>
@@ -2692,12 +2484,8 @@
       <c r="I54" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
       <c r="L54" s="9" t="n">
         <v>61003</v>
       </c>
@@ -2733,12 +2521,8 @@
       <c r="I55" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
       <c r="L55" s="9" t="n">
         <v>61004</v>
       </c>
@@ -2774,12 +2558,8 @@
       <c r="I56" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
       <c r="L56" s="9" t="n">
         <v>61005</v>
       </c>
@@ -2815,12 +2595,8 @@
       <c r="I57" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
       <c r="L57" s="9" t="n">
         <v>61006</v>
       </c>
@@ -2856,12 +2632,8 @@
       <c r="I58" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
       <c r="L58" s="9" t="n">
         <v>61007</v>
       </c>
@@ -2897,12 +2669,8 @@
       <c r="I59" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
       <c r="L59" s="9" t="n">
         <v>61008</v>
       </c>
@@ -2938,12 +2706,8 @@
       <c r="I60" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
       <c r="L60" s="9" t="n">
         <v>61009</v>
       </c>
@@ -2979,12 +2743,8 @@
       <c r="I61" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
       <c r="L61" s="9" t="n">
         <v>61010</v>
       </c>
@@ -3020,12 +2780,8 @@
       <c r="I62" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
       <c r="L62" s="5" t="n">
         <v>61001</v>
       </c>
@@ -3061,12 +2817,8 @@
       <c r="I63" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
       <c r="L63" s="5" t="n">
         <v>61002</v>
       </c>
@@ -3102,12 +2854,8 @@
       <c r="I64" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
       <c r="L64" s="5" t="n">
         <v>61003</v>
       </c>
@@ -3143,12 +2891,8 @@
       <c r="I65" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
       <c r="L65" s="5" t="n">
         <v>61004</v>
       </c>
@@ -3184,12 +2928,8 @@
       <c r="I66" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
       <c r="L66" s="5" t="n">
         <v>61005</v>
       </c>
@@ -3225,12 +2965,8 @@
       <c r="I67" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
       <c r="L67" s="5" t="n">
         <v>61006</v>
       </c>
@@ -3266,12 +3002,8 @@
       <c r="I68" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
       <c r="L68" s="5" t="n">
         <v>61007</v>
       </c>
@@ -3307,12 +3039,8 @@
       <c r="I69" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
       <c r="L69" s="5" t="n">
         <v>61008</v>
       </c>
@@ -3348,12 +3076,8 @@
       <c r="I70" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
       <c r="L70" s="5" t="n">
         <v>61009</v>
       </c>
@@ -3389,12 +3113,8 @@
       <c r="I71" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
       <c r="L71" s="5" t="n">
         <v>61010</v>
       </c>
@@ -3430,12 +3150,8 @@
       <c r="I72" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J72" s="9"/>
+      <c r="K72" s="9"/>
       <c r="L72" s="9" t="n">
         <v>61001</v>
       </c>
@@ -3471,12 +3187,8 @@
       <c r="I73" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9"/>
       <c r="L73" s="9" t="n">
         <v>61002</v>
       </c>
@@ -3512,12 +3224,8 @@
       <c r="I74" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J74" s="9"/>
+      <c r="K74" s="9"/>
       <c r="L74" s="9" t="n">
         <v>61003</v>
       </c>
@@ -3553,12 +3261,8 @@
       <c r="I75" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J75" s="9"/>
+      <c r="K75" s="9"/>
       <c r="L75" s="9" t="n">
         <v>61004</v>
       </c>
@@ -3594,12 +3298,8 @@
       <c r="I76" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J76" s="9"/>
+      <c r="K76" s="9"/>
       <c r="L76" s="9" t="n">
         <v>61005</v>
       </c>
@@ -3635,12 +3335,8 @@
       <c r="I77" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
       <c r="L77" s="9" t="n">
         <v>61006</v>
       </c>
@@ -3676,12 +3372,8 @@
       <c r="I78" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J78" s="9"/>
+      <c r="K78" s="9"/>
       <c r="L78" s="9" t="n">
         <v>61007</v>
       </c>
@@ -3717,12 +3409,8 @@
       <c r="I79" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J79" s="9"/>
+      <c r="K79" s="9"/>
       <c r="L79" s="9" t="n">
         <v>61008</v>
       </c>
@@ -3758,12 +3446,8 @@
       <c r="I80" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J80" s="9"/>
+      <c r="K80" s="9"/>
       <c r="L80" s="9" t="n">
         <v>61009</v>
       </c>
@@ -3799,12 +3483,8 @@
       <c r="I81" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
       <c r="L81" s="9" t="n">
         <v>61010</v>
       </c>
@@ -3840,12 +3520,8 @@
       <c r="I82" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
       <c r="L82" s="5" t="n">
         <v>61001</v>
       </c>
@@ -3881,12 +3557,8 @@
       <c r="I83" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J83" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
       <c r="L83" s="5" t="n">
         <v>61002</v>
       </c>
@@ -3922,12 +3594,8 @@
       <c r="I84" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
       <c r="L84" s="5" t="n">
         <v>61003</v>
       </c>
@@ -3963,12 +3631,8 @@
       <c r="I85" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
       <c r="L85" s="5" t="n">
         <v>61004</v>
       </c>
@@ -4004,12 +3668,8 @@
       <c r="I86" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
       <c r="L86" s="5" t="n">
         <v>61005</v>
       </c>
@@ -4045,12 +3705,8 @@
       <c r="I87" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
       <c r="L87" s="5" t="n">
         <v>61006</v>
       </c>
@@ -4086,12 +3742,8 @@
       <c r="I88" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
       <c r="L88" s="5" t="n">
         <v>61007</v>
       </c>
@@ -4127,12 +3779,8 @@
       <c r="I89" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
       <c r="L89" s="5" t="n">
         <v>61008</v>
       </c>
@@ -4168,12 +3816,8 @@
       <c r="I90" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
       <c r="L90" s="5" t="n">
         <v>61009</v>
       </c>
@@ -4209,12 +3853,8 @@
       <c r="I91" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
       <c r="L91" s="5" t="n">
         <v>61010</v>
       </c>
@@ -4250,12 +3890,8 @@
       <c r="I92" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J92" s="9"/>
+      <c r="K92" s="9"/>
       <c r="L92" s="9" t="n">
         <v>61001</v>
       </c>
@@ -4291,12 +3927,8 @@
       <c r="I93" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J93" s="9"/>
+      <c r="K93" s="9"/>
       <c r="L93" s="9" t="n">
         <v>61002</v>
       </c>
@@ -4332,12 +3964,8 @@
       <c r="I94" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J94" s="9"/>
+      <c r="K94" s="9"/>
       <c r="L94" s="9" t="n">
         <v>61003</v>
       </c>
@@ -4373,12 +4001,8 @@
       <c r="I95" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J95" s="9"/>
+      <c r="K95" s="9"/>
       <c r="L95" s="9" t="n">
         <v>61004</v>
       </c>
@@ -4414,12 +4038,8 @@
       <c r="I96" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J96" s="9"/>
+      <c r="K96" s="9"/>
       <c r="L96" s="9" t="n">
         <v>61005</v>
       </c>
@@ -4455,12 +4075,8 @@
       <c r="I97" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J97" s="9"/>
+      <c r="K97" s="9"/>
       <c r="L97" s="9" t="n">
         <v>61006</v>
       </c>
@@ -4496,12 +4112,8 @@
       <c r="I98" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9"/>
       <c r="L98" s="9" t="n">
         <v>61007</v>
       </c>
@@ -4537,12 +4149,8 @@
       <c r="I99" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J99" s="9"/>
+      <c r="K99" s="9"/>
       <c r="L99" s="9" t="n">
         <v>61008</v>
       </c>
@@ -4578,12 +4186,8 @@
       <c r="I100" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J100" s="9"/>
+      <c r="K100" s="9"/>
       <c r="L100" s="9" t="n">
         <v>61009</v>
       </c>
@@ -4619,12 +4223,8 @@
       <c r="I101" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J101" s="9"/>
+      <c r="K101" s="9"/>
       <c r="L101" s="9" t="n">
         <v>61010</v>
       </c>
@@ -4660,12 +4260,8 @@
       <c r="I102" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J102" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5"/>
       <c r="L102" s="5" t="n">
         <v>61001</v>
       </c>
@@ -4701,12 +4297,8 @@
       <c r="I103" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J103" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5"/>
       <c r="L103" s="5" t="n">
         <v>61002</v>
       </c>
@@ -4742,12 +4334,8 @@
       <c r="I104" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J104" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
       <c r="L104" s="5" t="n">
         <v>61003</v>
       </c>
@@ -4783,12 +4371,8 @@
       <c r="I105" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J105" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5"/>
       <c r="L105" s="5" t="n">
         <v>61004</v>
       </c>
@@ -4824,12 +4408,8 @@
       <c r="I106" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
       <c r="L106" s="5" t="n">
         <v>61005</v>
       </c>
@@ -4865,12 +4445,8 @@
       <c r="I107" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J107" s="5"/>
+      <c r="K107" s="5"/>
       <c r="L107" s="5" t="n">
         <v>61006</v>
       </c>
@@ -4906,12 +4482,8 @@
       <c r="I108" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
       <c r="L108" s="5" t="n">
         <v>61007</v>
       </c>
@@ -4947,12 +4519,8 @@
       <c r="I109" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J109" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
       <c r="L109" s="5" t="n">
         <v>61008</v>
       </c>
@@ -4988,12 +4556,8 @@
       <c r="I110" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
       <c r="L110" s="5" t="n">
         <v>61009</v>
       </c>
@@ -5029,12 +4593,8 @@
       <c r="I111" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J111" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
       <c r="L111" s="5" t="n">
         <v>61010</v>
       </c>
@@ -5070,12 +4630,8 @@
       <c r="I112" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9"/>
       <c r="L112" s="9" t="n">
         <v>61001</v>
       </c>
@@ -5111,12 +4667,8 @@
       <c r="I113" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J113" s="9"/>
+      <c r="K113" s="9"/>
       <c r="L113" s="9" t="n">
         <v>61002</v>
       </c>
@@ -5152,12 +4704,8 @@
       <c r="I114" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J114" s="9"/>
+      <c r="K114" s="9"/>
       <c r="L114" s="9" t="n">
         <v>61003</v>
       </c>
@@ -5193,12 +4741,8 @@
       <c r="I115" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J115" s="9"/>
+      <c r="K115" s="9"/>
       <c r="L115" s="9" t="n">
         <v>61004</v>
       </c>
@@ -5234,12 +4778,8 @@
       <c r="I116" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J116" s="9"/>
+      <c r="K116" s="9"/>
       <c r="L116" s="9" t="n">
         <v>61005</v>
       </c>
@@ -5275,12 +4815,8 @@
       <c r="I117" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J117" s="9"/>
+      <c r="K117" s="9"/>
       <c r="L117" s="9" t="n">
         <v>61006</v>
       </c>
@@ -5316,12 +4852,8 @@
       <c r="I118" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J118" s="9"/>
+      <c r="K118" s="9"/>
       <c r="L118" s="9" t="n">
         <v>61007</v>
       </c>
@@ -5357,12 +4889,8 @@
       <c r="I119" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J119" s="9"/>
+      <c r="K119" s="9"/>
       <c r="L119" s="9" t="n">
         <v>61008</v>
       </c>
@@ -5398,12 +4926,8 @@
       <c r="I120" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J120" s="9"/>
+      <c r="K120" s="9"/>
       <c r="L120" s="9" t="n">
         <v>61009</v>
       </c>
@@ -5439,12 +4963,8 @@
       <c r="I121" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J121" s="9"/>
+      <c r="K121" s="9"/>
       <c r="L121" s="9" t="n">
         <v>61010</v>
       </c>
@@ -5480,12 +5000,8 @@
       <c r="I122" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J122" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J122" s="5"/>
+      <c r="K122" s="5"/>
       <c r="L122" s="5" t="n">
         <v>61001</v>
       </c>
@@ -5521,12 +5037,8 @@
       <c r="I123" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J123" s="5"/>
+      <c r="K123" s="5"/>
       <c r="L123" s="5" t="n">
         <v>61002</v>
       </c>
@@ -5562,12 +5074,8 @@
       <c r="I124" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J124" s="5"/>
+      <c r="K124" s="5"/>
       <c r="L124" s="5" t="n">
         <v>61003</v>
       </c>
@@ -5603,12 +5111,8 @@
       <c r="I125" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J125" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J125" s="5"/>
+      <c r="K125" s="5"/>
       <c r="L125" s="5" t="n">
         <v>61004</v>
       </c>
@@ -5644,12 +5148,8 @@
       <c r="I126" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J126" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J126" s="5"/>
+      <c r="K126" s="5"/>
       <c r="L126" s="5" t="n">
         <v>61005</v>
       </c>
@@ -5685,12 +5185,8 @@
       <c r="I127" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J127" s="5"/>
+      <c r="K127" s="5"/>
       <c r="L127" s="5" t="n">
         <v>61006</v>
       </c>
@@ -5726,12 +5222,8 @@
       <c r="I128" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J128" s="5"/>
+      <c r="K128" s="5"/>
       <c r="L128" s="5" t="n">
         <v>61007</v>
       </c>
@@ -5767,12 +5259,8 @@
       <c r="I129" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J129" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J129" s="5"/>
+      <c r="K129" s="5"/>
       <c r="L129" s="5" t="n">
         <v>61008</v>
       </c>
@@ -5808,12 +5296,8 @@
       <c r="I130" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J130" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J130" s="5"/>
+      <c r="K130" s="5"/>
       <c r="L130" s="5" t="n">
         <v>61009</v>
       </c>
@@ -5849,12 +5333,8 @@
       <c r="I131" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J131" s="5"/>
+      <c r="K131" s="5"/>
       <c r="L131" s="5" t="n">
         <v>61010</v>
       </c>
@@ -5890,12 +5370,8 @@
       <c r="I132" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J132" s="9"/>
+      <c r="K132" s="9"/>
       <c r="L132" s="9" t="n">
         <v>61001</v>
       </c>
@@ -5931,12 +5407,8 @@
       <c r="I133" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J133" s="9"/>
+      <c r="K133" s="9"/>
       <c r="L133" s="9" t="n">
         <v>61002</v>
       </c>
@@ -5972,12 +5444,8 @@
       <c r="I134" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J134" s="9"/>
+      <c r="K134" s="9"/>
       <c r="L134" s="9" t="n">
         <v>61003</v>
       </c>
@@ -6013,12 +5481,8 @@
       <c r="I135" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J135" s="9"/>
+      <c r="K135" s="9"/>
       <c r="L135" s="9" t="n">
         <v>61004</v>
       </c>
@@ -6054,12 +5518,8 @@
       <c r="I136" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J136" s="9"/>
+      <c r="K136" s="9"/>
       <c r="L136" s="9" t="n">
         <v>61005</v>
       </c>
@@ -6095,12 +5555,8 @@
       <c r="I137" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J137" s="9"/>
+      <c r="K137" s="9"/>
       <c r="L137" s="9" t="n">
         <v>61006</v>
       </c>
@@ -6136,12 +5592,8 @@
       <c r="I138" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J138" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J138" s="9"/>
+      <c r="K138" s="9"/>
       <c r="L138" s="9" t="n">
         <v>61007</v>
       </c>
@@ -6177,12 +5629,8 @@
       <c r="I139" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J139" s="9"/>
+      <c r="K139" s="9"/>
       <c r="L139" s="9" t="n">
         <v>61008</v>
       </c>
@@ -6218,12 +5666,8 @@
       <c r="I140" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J140" s="9"/>
+      <c r="K140" s="9"/>
       <c r="L140" s="9" t="n">
         <v>61009</v>
       </c>
@@ -6259,12 +5703,8 @@
       <c r="I141" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J141" s="9"/>
+      <c r="K141" s="9"/>
       <c r="L141" s="9" t="n">
         <v>61010</v>
       </c>
@@ -6300,12 +5740,8 @@
       <c r="I142" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J142" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J142" s="5"/>
+      <c r="K142" s="5"/>
       <c r="L142" s="5" t="n">
         <v>61001</v>
       </c>
@@ -6341,12 +5777,8 @@
       <c r="I143" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J143" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J143" s="5"/>
+      <c r="K143" s="5"/>
       <c r="L143" s="5" t="n">
         <v>61002</v>
       </c>
@@ -6382,12 +5814,8 @@
       <c r="I144" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J144" s="5"/>
+      <c r="K144" s="5"/>
       <c r="L144" s="5" t="n">
         <v>61003</v>
       </c>
@@ -6423,12 +5851,8 @@
       <c r="I145" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K145" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J145" s="5"/>
+      <c r="K145" s="5"/>
       <c r="L145" s="5" t="n">
         <v>61004</v>
       </c>
@@ -6464,12 +5888,8 @@
       <c r="I146" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J146" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J146" s="5"/>
+      <c r="K146" s="5"/>
       <c r="L146" s="5" t="n">
         <v>61005</v>
       </c>
@@ -6505,12 +5925,8 @@
       <c r="I147" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J147" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K147" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J147" s="5"/>
+      <c r="K147" s="5"/>
       <c r="L147" s="5" t="n">
         <v>61006</v>
       </c>
@@ -6546,12 +5962,8 @@
       <c r="I148" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J148" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J148" s="5"/>
+      <c r="K148" s="5"/>
       <c r="L148" s="5" t="n">
         <v>61007</v>
       </c>
@@ -6587,12 +5999,8 @@
       <c r="I149" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J149" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J149" s="5"/>
+      <c r="K149" s="5"/>
       <c r="L149" s="5" t="n">
         <v>61008</v>
       </c>
@@ -6628,12 +6036,8 @@
       <c r="I150" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J150" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J150" s="5"/>
+      <c r="K150" s="5"/>
       <c r="L150" s="5" t="n">
         <v>61009</v>
       </c>
@@ -6669,12 +6073,8 @@
       <c r="I151" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J151" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J151" s="5"/>
+      <c r="K151" s="5"/>
       <c r="L151" s="5" t="n">
         <v>61010</v>
       </c>
@@ -6710,12 +6110,8 @@
       <c r="I152" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J152" s="9"/>
+      <c r="K152" s="9"/>
       <c r="L152" s="9" t="n">
         <v>61001</v>
       </c>
@@ -6751,12 +6147,8 @@
       <c r="I153" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J153" s="9"/>
+      <c r="K153" s="9"/>
       <c r="L153" s="9" t="n">
         <v>61002</v>
       </c>
@@ -6792,12 +6184,8 @@
       <c r="I154" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K154" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J154" s="9"/>
+      <c r="K154" s="9"/>
       <c r="L154" s="9" t="n">
         <v>61003</v>
       </c>
@@ -6833,12 +6221,8 @@
       <c r="I155" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J155" s="9"/>
+      <c r="K155" s="9"/>
       <c r="L155" s="9" t="n">
         <v>61004</v>
       </c>
@@ -6874,12 +6258,8 @@
       <c r="I156" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J156" s="9"/>
+      <c r="K156" s="9"/>
       <c r="L156" s="9" t="n">
         <v>61005</v>
       </c>
@@ -6915,12 +6295,8 @@
       <c r="I157" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J157" s="9"/>
+      <c r="K157" s="9"/>
       <c r="L157" s="9" t="n">
         <v>61006</v>
       </c>
@@ -6956,12 +6332,8 @@
       <c r="I158" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J158" s="9"/>
+      <c r="K158" s="9"/>
       <c r="L158" s="9" t="n">
         <v>61007</v>
       </c>
@@ -6997,12 +6369,8 @@
       <c r="I159" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J159" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J159" s="9"/>
+      <c r="K159" s="9"/>
       <c r="L159" s="9" t="n">
         <v>61008</v>
       </c>
@@ -7038,12 +6406,8 @@
       <c r="I160" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J160" s="9"/>
+      <c r="K160" s="9"/>
       <c r="L160" s="9" t="n">
         <v>61009</v>
       </c>
@@ -7079,12 +6443,8 @@
       <c r="I161" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K161" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J161" s="9"/>
+      <c r="K161" s="9"/>
       <c r="L161" s="9" t="n">
         <v>61010</v>
       </c>
@@ -7120,12 +6480,8 @@
       <c r="I162" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J162" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K162" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J162" s="5"/>
+      <c r="K162" s="5"/>
       <c r="L162" s="5" t="n">
         <v>61001</v>
       </c>
@@ -7161,12 +6517,8 @@
       <c r="I163" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J163" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J163" s="5"/>
+      <c r="K163" s="5"/>
       <c r="L163" s="5" t="n">
         <v>61002</v>
       </c>
@@ -7202,12 +6554,8 @@
       <c r="I164" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J164" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J164" s="5"/>
+      <c r="K164" s="5"/>
       <c r="L164" s="5" t="n">
         <v>61003</v>
       </c>
@@ -7243,12 +6591,8 @@
       <c r="I165" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J165" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J165" s="5"/>
+      <c r="K165" s="5"/>
       <c r="L165" s="5" t="n">
         <v>61004</v>
       </c>
@@ -7284,12 +6628,8 @@
       <c r="I166" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J166" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J166" s="5"/>
+      <c r="K166" s="5"/>
       <c r="L166" s="5" t="n">
         <v>61005</v>
       </c>
@@ -7325,12 +6665,8 @@
       <c r="I167" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J167" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J167" s="5"/>
+      <c r="K167" s="5"/>
       <c r="L167" s="5" t="n">
         <v>61006</v>
       </c>
@@ -7366,12 +6702,8 @@
       <c r="I168" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J168" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J168" s="5"/>
+      <c r="K168" s="5"/>
       <c r="L168" s="5" t="n">
         <v>61007</v>
       </c>
@@ -7407,12 +6739,8 @@
       <c r="I169" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J169" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J169" s="5"/>
+      <c r="K169" s="5"/>
       <c r="L169" s="5" t="n">
         <v>61008</v>
       </c>
@@ -7448,12 +6776,8 @@
       <c r="I170" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J170" s="5"/>
+      <c r="K170" s="5"/>
       <c r="L170" s="5" t="n">
         <v>61009</v>
       </c>
@@ -7489,12 +6813,8 @@
       <c r="I171" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J171" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J171" s="5"/>
+      <c r="K171" s="5"/>
       <c r="L171" s="5" t="n">
         <v>61010</v>
       </c>
@@ -7530,12 +6850,8 @@
       <c r="I172" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J172" s="9"/>
+      <c r="K172" s="9"/>
       <c r="L172" s="9" t="n">
         <v>61001</v>
       </c>
@@ -7571,12 +6887,8 @@
       <c r="I173" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J173" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K173" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J173" s="9"/>
+      <c r="K173" s="9"/>
       <c r="L173" s="9" t="n">
         <v>61002</v>
       </c>
@@ -7612,12 +6924,8 @@
       <c r="I174" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K174" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J174" s="9"/>
+      <c r="K174" s="9"/>
       <c r="L174" s="9" t="n">
         <v>61003</v>
       </c>
@@ -7653,12 +6961,8 @@
       <c r="I175" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J175" s="9"/>
+      <c r="K175" s="9"/>
       <c r="L175" s="9" t="n">
         <v>61004</v>
       </c>
@@ -7694,12 +6998,8 @@
       <c r="I176" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J176" s="9"/>
+      <c r="K176" s="9"/>
       <c r="L176" s="9" t="n">
         <v>61005</v>
       </c>
@@ -7735,12 +7035,8 @@
       <c r="I177" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K177" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J177" s="9"/>
+      <c r="K177" s="9"/>
       <c r="L177" s="9" t="n">
         <v>61006</v>
       </c>
@@ -7776,12 +7072,8 @@
       <c r="I178" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J178" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J178" s="9"/>
+      <c r="K178" s="9"/>
       <c r="L178" s="9" t="n">
         <v>61007</v>
       </c>
@@ -7817,12 +7109,8 @@
       <c r="I179" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K179" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J179" s="9"/>
+      <c r="K179" s="9"/>
       <c r="L179" s="9" t="n">
         <v>61008</v>
       </c>
@@ -7858,12 +7146,8 @@
       <c r="I180" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J180" s="9"/>
+      <c r="K180" s="9"/>
       <c r="L180" s="9" t="n">
         <v>61009</v>
       </c>
@@ -7899,12 +7183,8 @@
       <c r="I181" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J181" s="9"/>
+      <c r="K181" s="9"/>
       <c r="L181" s="9" t="n">
         <v>61010</v>
       </c>
@@ -7940,12 +7220,8 @@
       <c r="I182" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J182" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J182" s="5"/>
+      <c r="K182" s="5"/>
       <c r="L182" s="5" t="n">
         <v>61001</v>
       </c>
@@ -7981,12 +7257,8 @@
       <c r="I183" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J183" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J183" s="5"/>
+      <c r="K183" s="5"/>
       <c r="L183" s="5" t="n">
         <v>61002</v>
       </c>
@@ -8022,12 +7294,8 @@
       <c r="I184" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J184" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J184" s="5"/>
+      <c r="K184" s="5"/>
       <c r="L184" s="5" t="n">
         <v>61003</v>
       </c>
@@ -8063,12 +7331,8 @@
       <c r="I185" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J185" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K185" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J185" s="5"/>
+      <c r="K185" s="5"/>
       <c r="L185" s="5" t="n">
         <v>61004</v>
       </c>
@@ -8104,12 +7368,8 @@
       <c r="I186" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J186" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K186" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J186" s="5"/>
+      <c r="K186" s="5"/>
       <c r="L186" s="5" t="n">
         <v>61005</v>
       </c>
@@ -8145,12 +7405,8 @@
       <c r="I187" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J187" s="5"/>
+      <c r="K187" s="5"/>
       <c r="L187" s="5" t="n">
         <v>61006</v>
       </c>
@@ -8186,12 +7442,8 @@
       <c r="I188" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J188" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J188" s="5"/>
+      <c r="K188" s="5"/>
       <c r="L188" s="5" t="n">
         <v>61007</v>
       </c>
@@ -8227,12 +7479,8 @@
       <c r="I189" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J189" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J189" s="5"/>
+      <c r="K189" s="5"/>
       <c r="L189" s="5" t="n">
         <v>61008</v>
       </c>
@@ -8268,12 +7516,8 @@
       <c r="I190" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="J190" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K190" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J190" s="5"/>
+      <c r="K190" s="5"/>
       <c r="L190" s="5" t="n">
         <v>61009</v>
       </c>
@@ -8309,12 +7553,8 @@
       <c r="I191" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="J191" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K191" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="J191" s="5"/>
+      <c r="K191" s="5"/>
       <c r="L191" s="5" t="n">
         <v>61010</v>
       </c>
@@ -8350,12 +7590,8 @@
       <c r="I192" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J192" s="9"/>
+      <c r="K192" s="9"/>
       <c r="L192" s="9" t="n">
         <v>61001</v>
       </c>
@@ -8391,12 +7627,8 @@
       <c r="I193" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J193" s="9"/>
+      <c r="K193" s="9"/>
       <c r="L193" s="9" t="n">
         <v>61002</v>
       </c>
@@ -8432,12 +7664,8 @@
       <c r="I194" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J194" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J194" s="9"/>
+      <c r="K194" s="9"/>
       <c r="L194" s="9" t="n">
         <v>61003</v>
       </c>
@@ -8473,12 +7701,8 @@
       <c r="I195" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J195" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K195" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J195" s="9"/>
+      <c r="K195" s="9"/>
       <c r="L195" s="9" t="n">
         <v>61004</v>
       </c>
@@ -8514,12 +7738,8 @@
       <c r="I196" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J196" s="9"/>
+      <c r="K196" s="9"/>
       <c r="L196" s="9" t="n">
         <v>61005</v>
       </c>
@@ -8555,12 +7775,8 @@
       <c r="I197" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J197" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J197" s="9"/>
+      <c r="K197" s="9"/>
       <c r="L197" s="9" t="n">
         <v>61006</v>
       </c>
@@ -8596,12 +7812,8 @@
       <c r="I198" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J198" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J198" s="9"/>
+      <c r="K198" s="9"/>
       <c r="L198" s="9" t="n">
         <v>61007</v>
       </c>
@@ -8637,12 +7849,8 @@
       <c r="I199" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J199" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J199" s="9"/>
+      <c r="K199" s="9"/>
       <c r="L199" s="9" t="n">
         <v>61008</v>
       </c>
@@ -8678,12 +7886,8 @@
       <c r="I200" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="J200" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J200" s="9"/>
+      <c r="K200" s="9"/>
       <c r="L200" s="9" t="n">
         <v>61009</v>
       </c>
@@ -8719,12 +7923,8 @@
       <c r="I201" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="J201" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" s="9" t="n">
-        <v>0</v>
-      </c>
+      <c r="J201" s="9"/>
+      <c r="K201" s="9"/>
       <c r="L201" s="9" t="n">
         <v>61010</v>
       </c>
